--- a/outputs/52541.xlsx
+++ b/outputs/52541.xlsx
@@ -197,75 +197,75 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="2" borderId="0" xfId="17" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="0" xfId="17" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="17" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="17" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -502,7 +502,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J13"/>
-  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.16015625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.17"/>
@@ -596,7 +596,7 @@
       </c>
       <c r="I6" s="15" t="n">
         <f aca="false">IF(Table2[[#This Row],[Amount Outstanding]]=0,"",TODAY()-Table2[[#This Row],[Due Date]])</f>
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="J6" s="9" t="str">
         <f aca="false">IF(Table2[[#This Row],[Amount Outstanding]]&lt;0,"Prepaid",IF(Table2[[#This Row],[Over Due Days]]="","",IF(Table2[[#This Row],[Over Due Days]]&lt;90,"Call Customer","Bad Debts")))</f>
@@ -632,7 +632,7 @@
       </c>
       <c r="I7" s="15" t="n">
         <f aca="false">IF(Table2[[#This Row],[Amount Outstanding]]=0,"",TODAY()-Table2[[#This Row],[Due Date]])</f>
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="J7" s="9" t="str">
         <f aca="false">IF(Table2[[#This Row],[Amount Outstanding]]&lt;0,"Prepaid",IF(Table2[[#This Row],[Over Due Days]]="","",IF(Table2[[#This Row],[Over Due Days]]&lt;90,"Call Customer","Bad Debts")))</f>
@@ -668,7 +668,7 @@
       </c>
       <c r="I8" s="15" t="n">
         <f aca="false">IF(Table2[[#This Row],[Amount Outstanding]]=0,"",TODAY()-Table2[[#This Row],[Due Date]])</f>
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="J8" s="9" t="str">
         <f aca="false">IF(Table2[[#This Row],[Amount Outstanding]]&lt;0,"Prepaid",IF(Table2[[#This Row],[Over Due Days]]="","",IF(Table2[[#This Row],[Over Due Days]]&lt;90,"Call Customer","Bad Debts")))</f>
@@ -704,7 +704,7 @@
       </c>
       <c r="I9" s="15" t="n">
         <f aca="false">IF(Table2[[#This Row],[Amount Outstanding]]=0,"",TODAY()-Table2[[#This Row],[Due Date]])</f>
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="J9" s="9" t="str">
         <f aca="false">IF(Table2[[#This Row],[Amount Outstanding]]&lt;0,"Prepaid",IF(Table2[[#This Row],[Over Due Days]]="","",IF(Table2[[#This Row],[Over Due Days]]&lt;90,"Call Customer","Bad Debts")))</f>
@@ -740,7 +740,7 @@
       </c>
       <c r="I10" s="15" t="n">
         <f aca="false">IF(Table2[[#This Row],[Amount Outstanding]]=0,"",TODAY()-Table2[[#This Row],[Due Date]])</f>
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="J10" s="9" t="str">
         <f aca="false">IF(Table2[[#This Row],[Amount Outstanding]]&lt;0,"Prepaid",IF(Table2[[#This Row],[Over Due Days]]="","",IF(Table2[[#This Row],[Over Due Days]]&lt;90,"Call Customer","Bad Debts")))</f>
